--- a/Result/checksun_type/配電管理設施.xlsx
+++ b/Result/checksun_type/配電管理設施.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>22.87</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>22.81</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>24.14</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>24.14</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>2958.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4457.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4457.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2724.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1743.66</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1743.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>876.2209420123108</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>2958</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2958.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>22.77</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>22.84</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>24.21</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>24.21</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>16997.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4064.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4064.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>2595.9</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1707.64</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1707.64</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>1104.14953416486</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>16997</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>16997.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>22.62</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>22.89</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>24.27</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>24.27</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>1110.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>776.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>776.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>982.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1400.4</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1400.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-113.8506746945286</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>1110</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1110.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>22.5</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>22.97</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>24.34</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>24.34</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>779.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>733.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>733</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>966.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1426.7</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1426.7</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-147.6063061117077</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>779</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>779.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>22.57</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>23.06</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>24.42</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>24.42</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>444.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>748.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>748.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>969.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1460.74</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1460.74</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-155.0926972036882</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>444</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>444.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>23.13</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>24.52</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>24.52</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>991.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>990.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>990.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1200.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1474.18</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1474.18</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-124.3556595778143</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>991</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>991.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>22.75</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>23.18</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>24.61</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>24.61</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>560.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1127.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1127.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1171.1</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1477.22</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1477.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-134.6114751273581</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>560</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>560.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>23.22</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>24.7</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>23.22</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>24.7</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>891.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1187.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1187.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1165.1</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1486.16</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1486.16</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-98.27651608644328</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>891</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>891.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>24.8</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>856.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1200.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1200.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>1263.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1491.8</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1491.8</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-78.32384188204969</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>856</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>856.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>22.62</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>23.3</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>24.9</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>1655.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1190.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1190.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>1310.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1534.8</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1534.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-43.27274152284258</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>1655</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>1655.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>22.51</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>23.32</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>25</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1676.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1410.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1410.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1283.0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1512.04</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1512.04</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-77.26142881244505</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1676</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1676.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>38.4</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>36.82</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>36.82</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>412691555.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>537923909.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>537923909.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>900938946.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1659061579.84</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1659061579.84</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-340302592.3089933</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>412691555</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>412691555.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>38.47000000000001</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>40.82</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>36.64</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>36.64</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>310248541.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>599768488.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>599768488.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>928128187.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1670591514.14</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1670591514.14</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-350213793.6451616</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>310248541</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>310248541.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>38.77</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>41.23</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>36.45</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>36.45</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>513519842.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>801315362.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>801315362</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>1051248202.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1665600635.94</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1665600635.94</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-340888979.9952178</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>513519842</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>513519842.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>39.48</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>41.57</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>36.28</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>36.28</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>713550342.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>891841131.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>891841131.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>1082622886.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1657373135.48</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1657373135.48</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-337172279.1740401</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>713550342</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>713550342.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>39.85</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>41.74</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>36.09</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>739609269.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>1019757089.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>1019757089</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>1110319268.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1644306482.46</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1644306482.46</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-341252678.7447135</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>739609269</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>739609269.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>40.25</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>41.89</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>35.86</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>35.86</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>721914447.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1263953982.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1263953982.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1189736298.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1630600534.88</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1630600534.88</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-337686253.2119358</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>721914447</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>721914447.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>40.26000000000001</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>41.89</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>35.66</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>35.66</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1317982910.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1256487886.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1256487886.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1241011466.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1617918320.18</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1617918320.18</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-318635262.4789698</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1317982910</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1317982910.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>40.13</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>41.78</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>35.42</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>966148690.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1301181042.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>1301181042.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1251335802.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1592827120.16</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1592827120.16</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-343904208.8076265</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>966148690</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>966148690.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>40.32</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>35.16</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>35.16</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>1353130129.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>1273404641.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>1273404641.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1399005126.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1574549387.44</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1574549387.44</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-330023886.819721</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>1353130129</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>1353130129.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>40.64</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>41.42</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>34.92</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>34.92</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1960593737.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1200881448.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1200881448</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1638996102.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1548989496.08</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1548989496.08</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-339870585.057723</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1960593737</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1960593737.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>40.71</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>41.09</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>34.65</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>34.65</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>684583968.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1115518613.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1115518613.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1826554323.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1511039872.0</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1511039872</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-406884448.2170932</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>684583968</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>684583968.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>99.47999999999999</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>102.82</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>105</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>103180579.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>116147614.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>116147614.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>176548720.3</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>201428975.56</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>201428975.56</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-25860202.92993152</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>103180579</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>103180579.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>98.94</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>103.24</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>105.06</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>103.24</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>105.06</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>78066930.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>134482037.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>134482037.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>193869170.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>205225010.12</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>205225010.12</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-24317788.82020301</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>78066930</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>78066930.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>98.72</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>103.7</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>105.23</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>105.23</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>136094275.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>162561404.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>162561404.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>195664628.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>209197245.52</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>209197245.52</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-18555099.52701217</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>136094275</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>136094275.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>98.9</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>104.3</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>105.44</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>105.44</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>116900919.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>222301963.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>222301963.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>191158060.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>220229469.28</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>220229469.28</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-15877219.6607748</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>116900919</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>116900919.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>99.6</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>104.8</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>105.6</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>146495369.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>240594220.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>240594220.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>198554746.8</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>221461486.3</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>221461486.3</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-9428202.435408056</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>146495369</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>146495369.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>100.4</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>105.28</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>105.69</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>105.28</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>105.69</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>194852695.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>236949826.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>236949826.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>211794368.0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>221171326.8</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>221171326.8</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-3049433.097905278</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>194852695</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>194852695.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>101.84</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>105.81</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>105.84</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>105.84</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>218463765.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>253256304.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>253256304</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>212975569.9</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>219688213.02</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>219688213.02</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>990860.7805953324</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>218463765</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>218463765.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>102.86</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>106.24</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>106.24</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>106</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>434797068.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>228767852.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>228767852.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>230869656.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>217695178.8</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>217695178.8</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>4197563.793432087</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>434797068</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>434797068.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>103.8</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>106.6</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>106.11</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>106.11</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>208362204.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>160014158.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>160014158.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>237292886.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>210329621.68</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>210329621.68</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-14549913.0737094</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>208362204</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>106.8</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>106.18</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>106.18</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>128273399.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>156515273.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>156515273.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>280273763.1</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>208482988.26</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>208482988.26</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-16551504.84556478</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>128273399</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>128273399.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>106.85</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>106.24</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>106.24</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>276385084.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>186638909.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>186638909.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>285043227.5</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>208948816.74</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>208948816.74</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-10238853.09658802</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>276385084</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>276385084.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>67.44000000000001</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>62.95</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>57.54</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>57.54</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>68305837.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>68193204.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>68193204</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>136229985.7</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>46606279.72</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>46606279.72</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-1579885.667524114</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>68305837</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>68305837.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>67.64000000000001</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>57.23</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>57.23</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>59064123.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>84222262.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>84222262.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>140379245.7</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>45652449.62</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>45652449.62</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>1268393.578065202</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>59064123</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>59064123.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>67.8</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>61.76</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>56.91</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>56.91</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>55041164.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>115240085.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>115240085.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>153170422.4</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>44737206.8</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>44737206.8</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>6282247.801119044</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>55041164</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>55041164.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>68.92</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>61.16</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>56.6</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>77457284.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>149719715.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>149719715</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>157079528.3</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>44057108.44</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>44057108.44</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>13651562.01972742</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>77457284</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>69.28</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>60.56</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>56.31</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>60.56</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>56.31</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>81097612.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>180244870.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>180244870.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>161062192.7</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>42670813.98</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>42670813.98</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>21289870.83132054</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>81097612</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>81097612.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>69.06</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>59.93</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>55.99</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>59.93</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>55.99</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>148451128.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>204266767.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>204266767.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>153514394.7</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>41211816.88</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>41211816.88</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>31051352.88962071</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>148451128</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>148451128.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>68.47999999999999</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>59.37</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>55.7</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>55.7</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>214153238.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>196536229.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>196536229.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>140950400.0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>38471387.22</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>38471387.22</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>36670902.22684878</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>214153238</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>214153238.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>67.32000000000001</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>58.69</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>55.39</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>55.39</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>227439313.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>191100759.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>191100759.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>120375958.7</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>34338500.78</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>34338500.78</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>36349642.98621568</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>227439313</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>227439313.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>64.8</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>57.81</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>54.98</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>54.98</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>230083062.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>164439341.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>164439341.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>98801936.3</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>30095348.66</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>30095348.66</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>33168991.64294642</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>230083062</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>230083062.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>62.72000000000001</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>57.11</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>54.65</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>54.65</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>201207096.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>141879514.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>141879514.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>76590805.2</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>26134633.24</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>26134633.24</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>27157338.34388511</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>201207096</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>201207096.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>60.27999999999999</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>56.46</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>54.4</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>109798437.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>102762022.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>102762022</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>57072853.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>22355997.5</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>22355997.5</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>20693210.76151591</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>109798437</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>109798437.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20055,11 +19791,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
           <t>2459</t>
@@ -20241,41 +19973,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr">
         <is>
           <t>0</t>
@@ -20296,20 +20024,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>0</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>0</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20050,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>0</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20219,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20403,11 @@
           <t>804.2</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>783.55</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>695.92</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>783.55</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>695.92</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20454,16 @@
           <t>3873207064.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>9792069338.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>9792069338.799999</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>6844419299.3</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>3738324553.72</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>3738324553.72</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20480,10 @@
           <t>1072087242.743657</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>3873207064</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>3873207064.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20649,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20833,11 @@
           <t>798.2</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>782.95</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>691.4</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>782.95</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>691.4</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20884,16 @@
           <t>6366567274.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>9789142521.8</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>9789142521.799999</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>6940776945.3</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>3685793658.42</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>3685793658.42</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20910,10 @@
           <t>1641726702.107907</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>6366567274</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>6366567274.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21079,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21263,11 @@
           <t>781.6</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>778.6</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>686.42</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>778.6</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>686.42</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21314,16 @@
           <t>32037210452.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>9363145708.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>9363145708.200001</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>6664202888.6</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>3594108024.84</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>3594108024.84</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21340,10 @@
           <t>2129718525.052984</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>32037210452</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>32037210452.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21509,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21693,11 @@
           <t>774.4</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>775.0</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>681.74</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>775</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>681.74</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21744,16 @@
           <t>3219178175.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>3630962812.8</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>3630962812.8</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>3679090269.2</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>2987313106.58</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>2987313106.58</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21770,10 @@
           <t>362270.0083417892</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>3219178175</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>3219178175.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21939,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22123,11 @@
           <t>776.6</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>770.9</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>677.66</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>770.9</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>677.66</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22174,16 @@
           <t>3464183729.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>3719056022.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>3719056022</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>3577925548.1</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>2944835131.88</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>2944835131.88</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22200,10 @@
           <t>46058139.97998571</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>3464183729</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>3464183729.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22369,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22553,11 @@
           <t>776.4</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>765.15</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>672.94</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>765.15</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>672.9400000000001</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22604,16 @@
           <t>3858572979.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>3896769259.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>3896769259.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>3649778255.7</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>2912273920.24</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>2912273920.24</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22630,10 @@
           <t>83442425.58304882</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>3858572979</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>3858572979.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22799,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22983,11 @@
           <t>782.0</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>760.5</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>668.4</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>760.5</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>668.4</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23034,16 @@
           <t>4236583206.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>4092411368.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>4092411368.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>3704598909.3</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>2852984228.02</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>2852984228.02</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23060,10 @@
           <t>91612470.1737442</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>4236583206</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>4236583206.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23229,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23413,11 @@
           <t>784.8</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>756.0</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>664.4</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>756</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>664.4</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23464,16 @@
           <t>3376295975.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>3965260069.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>3965260069</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>3671040265.3</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>2794575964.04</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>2794575964.04</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23490,10 @@
           <t>59510992.76138973</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>3376295975</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>3376295975.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23659,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23843,11 @@
           <t>778.8</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>750.4</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>660.04</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>750.4</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>660.04</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23894,16 @@
           <t>3659644221.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>3727217725.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>3727217725.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>3740494004.2</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>2769663405.96</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>2769663405.96</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23920,10 @@
           <t>103699978.6094055</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>3659644221</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>3659644221.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24089,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24273,11 @@
           <t>770.0</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>745.85</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>655.52</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>745.85</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>655.52</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24324,16 @@
           <t>4352749918.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>3436795074.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>3436795074.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>3814140943.9</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>2735034261.96</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>2735034261.96</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24350,10 @@
           <t>132764789.9419494</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>4352749918</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>4352749918.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24519,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24703,11 @@
           <t>759.2</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>739.85</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>651.0</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>739.85</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>651</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24754,16 @@
           <t>4836783524.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>3402787251.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>3402787251.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>3884644605.1</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>2738363958.58</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>2738363958.58</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24780,10 @@
           <t>95283024.66908503</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>4836783524</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>4836783524.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24949,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25133,11 @@
           <t>919.4</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>948.95</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>947.82</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>948.95</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>947.8200000000001</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25184,16 @@
           <t>10702402903.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>13777681330.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>13777681330.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>13184190874.5</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>14165986897.28</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>14165986897.28</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25210,10 @@
           <t>-288049536.2624874</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>10702402903</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>10702402903.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25379,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25563,11 @@
           <t>909.2</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>954.7</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>945.54</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>954.7</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>945.54</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25614,16 @@
           <t>9579043601.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>13831910429.6</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>13831910429.6</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>13509805904.0</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>14413977761.06</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>14413977761.06</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25640,10 @@
           <t>-94238805.57345963</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>9579043601</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>9579043601.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25809,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25993,11 @@
           <t>906.8</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>962.95</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>944.08</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>962.95</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>944.08</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26044,16 @@
           <t>16911194399.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>14386844246.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>14386844246.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>13675683609.2</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>14618581897.64</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>14618581897.64</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26070,10 @@
           <t>306359263.681345</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>16911194399</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>16911194399.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26239,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26423,11 @@
           <t>911.4</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>971.8</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>941.9</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>971.8</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>941.9</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26474,16 @@
           <t>15812987742.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>13146559354.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>13146559354.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>13118876980.5</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>14614553602.28</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>14614553602.28</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26500,10 @@
           <t>82113231.98530579</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>15812987742</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>15812987742.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26669,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26853,11 @@
           <t>916.8</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>977.55</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>938.52</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>977.55</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>938.52</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26904,16 @@
           <t>15882778006.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>13620510362.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>13620510362.4</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>12470961715.4</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>14466055493.78</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>14466055493.78</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26930,10 @@
           <t>-123505858.3299389</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>15882778006</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>15882778006.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27099,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27283,11 @@
           <t>917.6</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>980.85</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>933.96</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>980.85</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>933.96</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27334,16 @@
           <t>10973548400.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>12590700418.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>12590700418.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>11918833012.0</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>14368721493.28</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>14368721493.28</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27360,10 @@
           <t>-420314020.6970749</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>10973548400</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>10973548400.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27529,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27713,11 @@
           <t>932.2</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>987.15</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>929.9</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>987.15</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>929.9</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27764,16 @@
           <t>12353712685.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>13187701378.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>13187701378.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>12539817288.3</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>14292572173.18</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>14292572173.18</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27790,10 @@
           <t>-303325579.8395176</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>12353712685</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>12353712685.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27959,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28143,11 @@
           <t>947.0</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>993.0</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>925.54</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>993</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>925.54</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28194,16 @@
           <t>10709769939.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>12964522972.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>12964522972</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>13184192924.4</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>14209168625.62</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>14209168625.62</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28220,10 @@
           <t>-273240924.15588</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>10709769939</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>10709769939.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28389,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28573,11 @@
           <t>960.2</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>997.15</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>920.92</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>997.15</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>920.92</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28624,16 @@
           <t>18182742782.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>13091194606.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>13091194606.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>13748861147.6</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>14155319682.02</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>14155319682.02</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28650,10 @@
           <t>-44367517.38797188</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>18182742782</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>18182742782.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28819,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29003,11 @@
           <t>968.8</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>1002.3</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>916.24</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>916.24</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29054,16 @@
           <t>10733728288.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>11321413068.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>11321413068.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>14033372540.0</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>13994353884.38</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>13994353884.38</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29080,10 @@
           <t>-516496615.2771072</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>10733728288</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>10733728288.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29249,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29433,11 @@
           <t>972.8</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>1005.15</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>911.3</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>1005.15</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>911.3</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29484,16 @@
           <t>13958553198.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>11246965605.2</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>11246965605.2</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>15377407355.7</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>13940555876.02</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>13940555876.02</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29510,10 @@
           <t>-374411751.6445465</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>13958553198</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>13958553198.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29679,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29863,11 @@
           <t>156.3</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>164.85</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>168.36</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>164.85</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>168.36</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29914,16 @@
           <t>3170553681.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>4138082091.0</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>4138082091</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>4268507640.2</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>6060043081.46</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>6060043081.46</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29940,10 @@
           <t>-263552895.6884155</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>3170553681</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>3170553681.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30109,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30293,11 @@
           <t>155.3</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>166.68</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>168.5</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>166.68</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>168.5</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30344,16 @@
           <t>3561255788.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>4508528303.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>4508528303.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>4128239206.8</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>6523283246.84</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>6523283246.84</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30370,10 @@
           <t>-197408387.5697174</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>3561255788</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>3561255788.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30539,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30723,11 @@
           <t>155.3</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>168.38</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>168.5</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>168.38</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>168.5</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30774,16 @@
           <t>5330763891.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>5326173063.4</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>5326173063.4</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>4050371893.2</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>6516029437.64</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>6516029437.64</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30800,10 @@
           <t>-137726873.5940866</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>5330763891</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>5330763891.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30969,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31153,11 @@
           <t>156.8</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>169.72</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>168.21</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>169.72</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>168.21</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31204,16 @@
           <t>3892624091.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>4843786138.2</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>4843786138.2</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>3728171837.0</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>6576214335.28</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>6576214335.28</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31230,10 @@
           <t>-237138904.8933973</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>3892624091</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>3892624091.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31399,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31583,11 @@
           <t>158.6</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>170.58</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>167.82</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>170.58</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>167.82</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31634,16 @@
           <t>4735213004.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>4739633072.6</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>4739633072.6</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>3540693680.5</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>6556873375.6</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>6556873375.6</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31660,10 @@
           <t>-216600438.7176485</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>4735213004</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>4735213004.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31829,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32013,11 @@
           <t>159.5</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>170.95</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>167.23</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>170.95</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>167.23</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32064,16 @@
           <t>5022784742.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>4398933189.4</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>4398933189.4</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>3348452263.6</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>6518094899.78</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>6518094899.78</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32090,10 @@
           <t>-269801426.3338051</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>5022784742</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>5022784742.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32259,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32443,11 @@
           <t>162.1</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>171.55</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>166.67</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>171.55</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>166.67</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32494,16 @@
           <t>7649479589.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>3747950110.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>3747950110.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>3187753716.9</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>6448828659.12</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>6448828659.12</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32520,10 @@
           <t>-366978329.6306791</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>7649479589</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>7649479589.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32689,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32873,11 @@
           <t>164.7</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>172.05</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>166.08</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>172.05</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>166.08</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32924,16 @@
           <t>2918829265.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>2774570723.0</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>2774570723</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>3016948267.5</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>6307955645.82</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>6307955645.82</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32950,10 @@
           <t>-774127699.0322614</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>2918829265</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>2918829265.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33119,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33303,11 @@
           <t>166.0</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>172.2</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>165.33</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>165.33</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33354,16 @@
           <t>3371858763.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>2612557535.8</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>2612557535.8</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>3246709810.3</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>6279997636.12</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>6279997636.12</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33380,10 @@
           <t>-821266845.6405125</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>3371858763</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>3371858763.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33549,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33733,11 @@
           <t>166.8</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>172.52</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>164.6</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>172.52</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>164.6</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33784,16 @@
           <t>3031713588.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>2341754288.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>2341754288.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>3717183320.3</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>6247764195.28</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>6247764195.28</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33810,10 @@
           <t>-907816399.6651387</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>3031713588</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>3031713588.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33979,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34163,11 @@
           <t>167.7</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>172.38</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>163.91</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>172.38</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>163.91</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34214,16 @@
           <t>1767869347.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>2297971337.8</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>2297971337.8</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>5310238320.6</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>6248161668.22</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>6248161668.22</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34240,10 @@
           <t>-962592479.5337062</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>1767869347</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>1767869347.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34409,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34593,11 @@
           <t>701.8</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>734.15</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>644.12</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>734.15</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>644.12</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34644,16 @@
           <t>2145406818.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>4705713538.6</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>4705713538.6</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>2697328683.0</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>2381458909.08</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>2381458909.08</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34670,10 @@
           <t>47833880.16900253</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>2145406818</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>2145406818.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34839,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35023,11 @@
           <t>712.8</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>729.6</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>642.32</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>729.6</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>642.3200000000001</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35074,16 @@
           <t>2917531202.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>4446393537.2</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>4446393537.2</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>2537135784.1</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>2394527724.36</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>2394527724.36</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35100,10 @@
           <t>171300840.0050039</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>2917531202</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>2917531202.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35269,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35453,11 @@
           <t>718.0</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>726.45</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>641.18</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>726.45</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>641.1799999999999</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35504,16 @@
           <t>3308931687.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>3977678243.4</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>3977678243.4</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>2336901368.1</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>2356977274.04</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>2356977274.04</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35530,10 @@
           <t>258836711.484827</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>3308931687</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>3308931687.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35699,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35883,11 @@
           <t>724.4</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>720.75</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>639.48</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>720.75</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>639.48</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35934,16 @@
           <t>9396894111.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>3406595539.2</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>3406595539.2</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>2092972596.2</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>2319670873.56</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>2319670873.56</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35960,10 @@
           <t>332708021.9386873</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>9396894111</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>9396894111.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36129,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36313,11 @@
           <t>731.2</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>715.55</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>638.3</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>715.55</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>638.3</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36364,16 @@
           <t>5759803875.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>1689450518.2</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>1689450518.2</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>1272693479.4</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>2149905312.46</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>2149905312.46</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36390,10 @@
           <t>-225925652.1964645</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>5759803875</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>5759803875.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36559,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36743,11 @@
           <t>732.4</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>708.6</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>635.96</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>708.6</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>635.96</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36794,16 @@
           <t>848806811.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>688943827.4</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>688943827.4</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>860708905.5</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>2069337538.82</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>2069337538.82</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36820,10 @@
           <t>-626216745.2396646</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>848806811</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>848806811.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36989,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37173,11 @@
           <t>735.4</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>701.1</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>633.54</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>701.1</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>633.54</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37224,16 @@
           <t>573954733.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>627878031.0</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>627878031</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>1516353585.7</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>2106062606.14</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>2106062606.14</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37250,10 @@
           <t>-649518023.2571056</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>573954733</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>573954733.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37419,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37603,11 @@
           <t>745.6</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>695.2</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>631.48</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>695.2</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>631.48</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37654,16 @@
           <t>453518166.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>696124492.8</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>696124492.8</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>2883970531.7</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>2126707687.18</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>2126707687.18</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37680,10 @@
           <t>-630160054.0942674</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>453518166</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>453518166.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37849,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38033,11 @@
           <t>752.0</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>688.05</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>628.72</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>688.05</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>628.72</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38084,16 @@
           <t>811169006.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>779349653.2</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>779349653.2</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>4079717323.9</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>2168937186.34</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>2168937186.34</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38110,10 @@
           <t>-567096178.3225608</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>811169006</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>811169006.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38279,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38463,11 @@
           <t>756.8</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>681.7</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>626.7</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>681.7</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>626.7</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38514,16 @@
           <t>757270421.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>855936440.6</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>855936440.6</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>4864530439.2</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>2227082877.5</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>2227082877.5</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38540,10 @@
           <t>-495071225.1371737</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>757270421</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>757270421.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38709,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38893,11 @@
           <t>760.8</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>624.74</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>673</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>624.74</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38944,16 @@
           <t>543477829.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>1032473983.6</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>1032473983.6</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>5522062366.6</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>2292721646.52</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>2292721646.52</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38970,10 @@
           <t>-368722471.2960072</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>543477829</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>543477829.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39139,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39323,11 @@
           <t>150.6</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>149.25</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>153.56</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>149.25</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>153.56</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39374,16 @@
           <t>467298154.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>1091975503.2</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>1091975503.2</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>971699108.1</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>769361530.6</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>769361530.6</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39400,10 @@
           <t>-15119773.40763056</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>467298154</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>467298154.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39569,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39753,11 @@
           <t>150.6</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>149.15</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>153.79</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>149.15</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>153.79</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39804,16 @@
           <t>710824368.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>1337624644.6</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>1337624644.6</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>951778434.3</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>775873277.4</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>775873277.4</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39830,10 @@
           <t>31499619.18289268</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>710824368</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>710824368.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +39999,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40183,11 @@
           <t>150.2</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>149.18</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>154.09</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>149.18</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>154.09</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40234,16 @@
           <t>984361332.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>1371944247.6</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>1371944247.6</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>917139763.8</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>770428376.1</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>770428376.1</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40260,10 @@
           <t>70881670.69853663</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>984361332</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>984361332.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40429,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40613,11 @@
           <t>148.9</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>149.2</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>154.33</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>149.2</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>154.33</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40664,16 @@
           <t>1286525950.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>1232573788.2</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>1232573788.2</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>862961176.8</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>763733625.74</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>763733625.74</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40690,10 @@
           <t>95302724.1959374</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>1286525950</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>1286525950.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40859,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41043,11 @@
           <t>147.8</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>149.2</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>154.58</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>149.2</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>154.58</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41094,16 @@
           <t>2010867712.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>1072694303.0</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>1072694303</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>856900855.0</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>752922533.34</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>752922533.34</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41120,10 @@
           <t>94411494.2566551</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>2010867712</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>2010867712.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41289,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41473,11 @@
           <t>147.6</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>149.32</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>154.87</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>149.32</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>154.87</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41524,16 @@
           <t>1695543861.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>851422713.0</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>851422713</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>685544317.2</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>751668929.8</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>751668929.8</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41550,10 @@
           <t>12158423.61994255</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>1695543861</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>1695543861.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41719,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41903,11 @@
           <t>146.3</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>149.52</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>155.2</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>149.52</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>155.2</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41954,16 @@
           <t>882422383.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>565932224.0</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>565932224</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>581506824.1</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>740084780.12</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>740084780.12</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41980,10 @@
           <t>-71995494.09750187</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>882422383</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>882422383.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42149,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42333,11 @@
           <t>145.7</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>149.88</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>155.56</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>149.88</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>155.56</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42384,16 @@
           <t>287509035.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>462335280.0</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>462335280</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>605251513.7</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>735380608.92</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>735380608.92</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42410,10 @@
           <t>-102523950.5475115</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>287509035</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>287509035.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42579,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42763,11 @@
           <t>145.6</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>150.48</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>155.9</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>150.48</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>155.9</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42814,16 @@
           <t>487128524.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>493348565.4</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>493348565.4</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>870934906.4</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>755782564.6</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>755782564.6</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42840,10 @@
           <t>-78733745.67082834</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>487128524</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>487128524.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43009,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43193,11 @@
           <t>145.4</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>151.1</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>156.28</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>151.1</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>156.28</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43244,16 @@
           <t>904509762.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>641107407.0</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>641107407</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>1218580183.3</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>785438747.86</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>785438747.86</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43270,10 @@
           <t>-63323621.60875154</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>904509762</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>904509762.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43439,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43623,11 @@
           <t>145.6</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>151.43</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>156.71</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>151.43</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>156.71</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43674,16 @@
           <t>268091416.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>519665921.4</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>519665921.4</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>1219128474.1</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>811875622.62</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>811875622.62</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43700,10 @@
           <t>-83767019.10547185</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>268091416</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>268091416.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
